--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>199</v>
+        <v>302</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>137</v>
+        <v>305</v>
       </c>
       <c r="D3">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E3">
-        <v>142</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>305</v>
       </c>
       <c r="D3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>426</v>
